--- a/database.xlsx
+++ b/database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/serena/Desktop/Hunter CRM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA89F9A3-C2B0-034D-B9C0-AEE4D62D508E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A19A0F2A-A6A4-3A40-A082-00F2B9EE729B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="37">
   <si>
     <t>date</t>
   </si>
@@ -139,6 +139,15 @@
   </si>
   <si>
     <t>SMS #1 What to Expect (EOI &amp; Build)</t>
+  </si>
+  <si>
+    <t>EDM #3: What does 360kW of power mean? (Reservation)</t>
+  </si>
+  <si>
+    <t>EDM #3: What does 360kW of power mean? (Build)</t>
+  </si>
+  <si>
+    <t>EDM #3: Hunter Pro vs Hunter X (EOI)</t>
   </si>
 </sst>
 </file>
@@ -207,12 +216,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -224,6 +232,10 @@
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -526,12 +538,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="23.33203125" customWidth="1"/>
+    <col min="3" max="3" width="42.1640625" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
     <col min="5" max="8" width="14" customWidth="1"/>
     <col min="9" max="12" width="17" customWidth="1"/>
@@ -546,7 +558,7 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>17</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -586,56 +598,56 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A2" s="2">
-        <v>46169</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="2" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="7">
+        <v>46170</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="8">
         <v>68</v>
       </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
+      <c r="E2" s="8">
+        <v>0</v>
+      </c>
+      <c r="F2" s="8">
         <v>68</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="8">
         <v>68</v>
       </c>
-      <c r="H2">
-        <v>44</v>
-      </c>
-      <c r="I2" s="6">
-        <v>0.64700000000000002</v>
-      </c>
-      <c r="J2">
-        <v>18</v>
-      </c>
-      <c r="K2" s="6">
-        <v>0.26500000000000001</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2" s="7">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2" s="7">
+      <c r="H2" s="8">
+        <v>47</v>
+      </c>
+      <c r="I2" s="9">
+        <v>0.69099999999999995</v>
+      </c>
+      <c r="J2" s="8">
+        <v>19</v>
+      </c>
+      <c r="K2" s="9">
+        <v>0.27900000000000003</v>
+      </c>
+      <c r="L2" s="8">
+        <v>2</v>
+      </c>
+      <c r="M2" s="9">
+        <v>2.9399999999999999E-2</v>
+      </c>
+      <c r="N2" s="8">
+        <v>0</v>
+      </c>
+      <c r="O2" s="10">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A3" s="2">
-        <v>46169</v>
+      <c r="A3" s="7">
+        <v>46170</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
@@ -656,33 +668,33 @@
         <v>102</v>
       </c>
       <c r="H3">
-        <v>45</v>
-      </c>
-      <c r="I3" s="6">
-        <v>0.30399999999999999</v>
+        <v>32</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0.314</v>
       </c>
       <c r="J3">
-        <v>12</v>
-      </c>
-      <c r="K3" s="6">
-        <v>0.11799999999999999</v>
+        <v>13</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0.127</v>
       </c>
       <c r="L3">
         <v>0</v>
       </c>
-      <c r="M3" s="7">
+      <c r="M3" s="6">
         <v>0</v>
       </c>
       <c r="N3">
         <v>0</v>
       </c>
-      <c r="O3" s="7">
+      <c r="O3" s="6">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A4" s="2">
-        <v>46169</v>
+      <c r="A4" s="7">
+        <v>46170</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
@@ -703,33 +715,33 @@
         <v>866</v>
       </c>
       <c r="H4">
-        <v>290</v>
-      </c>
-      <c r="I4" s="6">
-        <v>0.33500000000000002</v>
+        <v>294</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0.33900000000000002</v>
       </c>
       <c r="J4">
-        <v>79</v>
-      </c>
-      <c r="K4" s="6">
-        <v>9.0999999999999998E-2</v>
+        <v>83</v>
+      </c>
+      <c r="K4" s="5">
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="L4">
         <v>6</v>
       </c>
-      <c r="M4" s="6">
+      <c r="M4" s="5">
         <v>6.8999999999999999E-3</v>
       </c>
       <c r="N4">
         <v>1</v>
       </c>
-      <c r="O4" s="6">
+      <c r="O4" s="5">
         <v>1.1999999999999999E-3</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A5" s="2">
-        <v>46169</v>
+      <c r="A5" s="7">
+        <v>46170</v>
       </c>
       <c r="B5" t="s">
         <v>30</v>
@@ -740,6 +752,9 @@
       <c r="D5">
         <v>68</v>
       </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
       <c r="F5">
         <v>68</v>
       </c>
@@ -749,19 +764,19 @@
       <c r="J5">
         <v>38</v>
       </c>
-      <c r="K5" s="6">
+      <c r="K5" s="5">
         <v>0.57599999999999996</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
-      <c r="M5" s="7">
+      <c r="M5" s="6">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A6" s="2">
-        <v>46169</v>
+      <c r="A6" s="7">
+        <v>46170</v>
       </c>
       <c r="B6" t="s">
         <v>32</v>
@@ -772,6 +787,9 @@
       <c r="D6">
         <v>752</v>
       </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
       <c r="F6">
         <v>752</v>
       </c>
@@ -781,18 +799,94 @@
       <c r="J6">
         <v>302</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="5">
         <v>0.41199999999999998</v>
       </c>
       <c r="L6">
         <v>25</v>
       </c>
-      <c r="M6" s="6">
+      <c r="M6" s="5">
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A7" s="2"/>
+    <row r="7" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="7">
+        <v>46177</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="8">
+        <v>69</v>
+      </c>
+      <c r="E7" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A8" s="7">
+        <v>46177</v>
+      </c>
+      <c r="B8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8">
+        <v>110</v>
+      </c>
+      <c r="E8" s="8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A9" s="7">
+        <v>46177</v>
+      </c>
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9">
+        <v>890</v>
+      </c>
+      <c r="E9" s="8">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A10" s="7">
+        <v>46177</v>
+      </c>
+      <c r="B10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A11" s="7">
+        <v>46177</v>
+      </c>
+      <c r="B11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11">
+        <v>40</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:M4" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -811,58 +905,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="4" t="s">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>16</v>
       </c>
     </row>

--- a/database.xlsx
+++ b/database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/serena/Desktop/Hunter CRM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A19A0F2A-A6A4-3A40-A082-00F2B9EE729B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B47D4F9-0892-CA43-ABCB-F6B3AC2F63B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -216,7 +216,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -232,10 +232,7 @@
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -598,50 +595,50 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
         <v>46170</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" t="s">
         <v>28</v>
       </c>
-      <c r="D2" s="8">
+      <c r="D2">
         <v>68</v>
       </c>
-      <c r="E2" s="8">
-        <v>0</v>
-      </c>
-      <c r="F2" s="8">
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>68</v>
       </c>
-      <c r="G2" s="8">
+      <c r="G2">
         <v>68</v>
       </c>
-      <c r="H2" s="8">
+      <c r="H2">
         <v>47</v>
       </c>
-      <c r="I2" s="9">
+      <c r="I2" s="5">
         <v>0.69099999999999995</v>
       </c>
-      <c r="J2" s="8">
+      <c r="J2">
         <v>19</v>
       </c>
-      <c r="K2" s="9">
+      <c r="K2" s="5">
         <v>0.27900000000000003</v>
       </c>
-      <c r="L2" s="8">
+      <c r="L2">
         <v>2</v>
       </c>
-      <c r="M2" s="9">
+      <c r="M2" s="5">
         <v>2.9399999999999999E-2</v>
       </c>
-      <c r="N2" s="8">
-        <v>0</v>
-      </c>
-      <c r="O2" s="10">
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2" s="6">
         <v>0</v>
       </c>
     </row>
@@ -809,21 +806,51 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="7">
         <v>46177</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7">
         <v>69</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7">
         <v>3</v>
+      </c>
+      <c r="F7">
+        <v>69</v>
+      </c>
+      <c r="G7">
+        <v>69</v>
+      </c>
+      <c r="H7">
+        <v>50</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0.72499999999999998</v>
+      </c>
+      <c r="J7">
+        <v>22</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0.31900000000000001</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7" s="6">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7" s="6">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.2">
@@ -839,8 +866,38 @@
       <c r="D8">
         <v>110</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8">
         <v>7</v>
+      </c>
+      <c r="F8">
+        <v>110</v>
+      </c>
+      <c r="G8">
+        <v>110</v>
+      </c>
+      <c r="H8">
+        <v>32</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0.29099999999999998</v>
+      </c>
+      <c r="J8">
+        <v>8</v>
+      </c>
+      <c r="K8" s="5">
+        <v>7.2999999999999995E-2</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8" s="5">
+        <v>9.1000000000000004E-3</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8" s="6">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
@@ -856,8 +913,38 @@
       <c r="D9">
         <v>890</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9">
         <v>29</v>
+      </c>
+      <c r="F9">
+        <v>890</v>
+      </c>
+      <c r="G9">
+        <v>890</v>
+      </c>
+      <c r="H9">
+        <v>305</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0.34300000000000003</v>
+      </c>
+      <c r="J9">
+        <v>163</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0.183</v>
+      </c>
+      <c r="L9">
+        <v>4</v>
+      </c>
+      <c r="M9" s="5">
+        <v>4.4999999999999997E-3</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9" s="6">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.2">
@@ -873,6 +960,24 @@
       <c r="D10">
         <v>3</v>
       </c>
+      <c r="F10">
+        <v>3</v>
+      </c>
+      <c r="G10">
+        <v>3</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" s="7">
@@ -886,6 +991,25 @@
       </c>
       <c r="D11">
         <v>40</v>
+      </c>
+      <c r="F11">
+        <v>40</v>
+      </c>
+      <c r="G11">
+        <f>40*0.975</f>
+        <v>39</v>
+      </c>
+      <c r="J11">
+        <v>14</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0.35899999999999999</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11" s="6">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/database.xlsx
+++ b/database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/serena/Desktop/Hunter CRM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B47D4F9-0892-CA43-ABCB-F6B3AC2F63B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24E775AF-C52F-5140-B241-04F4BC4F8887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -618,10 +618,10 @@
         <v>68</v>
       </c>
       <c r="H2">
-        <v>47</v>
+        <v>137</v>
       </c>
       <c r="I2" s="5">
-        <v>0.69099999999999995</v>
+        <v>0.80879999999999996</v>
       </c>
       <c r="J2">
         <v>19</v>
@@ -665,16 +665,16 @@
         <v>102</v>
       </c>
       <c r="H3">
-        <v>32</v>
+        <v>72</v>
       </c>
       <c r="I3" s="5">
         <v>0.314</v>
       </c>
       <c r="J3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K3" s="5">
-        <v>0.127</v>
+        <v>0.13730000000000001</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -712,16 +712,16 @@
         <v>866</v>
       </c>
       <c r="H4">
-        <v>294</v>
+        <v>750</v>
       </c>
       <c r="I4" s="5">
-        <v>0.33900000000000002</v>
+        <v>0.47920000000000001</v>
       </c>
       <c r="J4">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="K4" s="5">
-        <v>9.6000000000000002E-2</v>
+        <v>0.1062</v>
       </c>
       <c r="L4">
         <v>6</v>

--- a/database.xlsx
+++ b/database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/serena/Desktop/Hunter CRM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24E775AF-C52F-5140-B241-04F4BC4F8887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4EC0303-DCDD-3A45-936B-5F4AC29516F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="40">
   <si>
     <t>date</t>
   </si>
@@ -148,6 +148,15 @@
   </si>
   <si>
     <t>EDM #3: Hunter Pro vs Hunter X (EOI)</t>
+  </si>
+  <si>
+    <t>EDM #4: Battery Charging (Build)</t>
+  </si>
+  <si>
+    <t>EDM #4: Battery Charging (EOI)</t>
+  </si>
+  <si>
+    <t>EDM #4: Battery Charging (Reserve)</t>
   </si>
 </sst>
 </file>
@@ -535,7 +544,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1010,6 +1019,57 @@
       </c>
       <c r="M11" s="6">
         <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A12" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12">
+        <v>72</v>
+      </c>
+      <c r="E12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A13" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13">
+        <v>113</v>
+      </c>
+      <c r="E13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A14" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14">
+        <v>895</v>
+      </c>
+      <c r="E14">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/database.xlsx
+++ b/database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/serena/Desktop/Hunter CRM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4EC0303-DCDD-3A45-936B-5F4AC29516F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB436F67-04DD-6A44-8EF4-C1B1DFF665B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/database.xlsx
+++ b/database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/serena/Desktop/Hunter CRM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB436F67-04DD-6A44-8EF4-C1B1DFF665B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2CAC9BC-ABED-2B4F-86B5-C5A4B12C3872}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="audience_daily_snapshot" sheetId="1" r:id="rId1"/>

--- a/database.xlsx
+++ b/database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/serena/Desktop/Hunter CRM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2CAC9BC-ABED-2B4F-86B5-C5A4B12C3872}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C088235E-F2C0-5949-9794-4C1BE61D901F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="audience_daily_snapshot" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="40">
   <si>
     <t>date</t>
   </si>
@@ -544,7 +544,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1070,6 +1070,84 @@
       </c>
       <c r="E14">
         <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A15" s="7">
+        <v>46185</v>
+      </c>
+      <c r="B15" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15">
+        <v>2</v>
+      </c>
+      <c r="F15">
+        <v>2</v>
+      </c>
+      <c r="G15">
+        <v>2</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15" s="6">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A16" s="7">
+        <v>46185</v>
+      </c>
+      <c r="B16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16">
+        <v>36</v>
+      </c>
+      <c r="F16">
+        <v>36</v>
+      </c>
+      <c r="G16">
+        <v>36</v>
+      </c>
+      <c r="J16">
+        <v>14</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0.38900000000000001</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" s="7">
+        <v>46188</v>
+      </c>
+      <c r="B17" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/database.xlsx
+++ b/database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/serena/Desktop/Hunter CRM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C088235E-F2C0-5949-9794-4C1BE61D901F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE0DFFFF-D31A-EA4B-9214-60CA17BC0F6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="43">
   <si>
     <t>date</t>
   </si>
@@ -157,6 +157,15 @@
   </si>
   <si>
     <t>EDM #4: Battery Charging (Reserve)</t>
+  </si>
+  <si>
+    <t>EDM #3: What does 360kW of power mean? (EOI)</t>
+  </si>
+  <si>
+    <t>EDM #3: Hunter Pro vs Hunter X (Build)</t>
+  </si>
+  <si>
+    <t>EDM #5: Off-Road Capability (Reservation)</t>
   </si>
 </sst>
 </file>
@@ -544,7 +553,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1037,6 +1046,36 @@
       <c r="E12">
         <v>3</v>
       </c>
+      <c r="F12">
+        <v>72</v>
+      </c>
+      <c r="G12">
+        <v>72</v>
+      </c>
+      <c r="H12">
+        <v>49</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0.68100000000000005</v>
+      </c>
+      <c r="J12">
+        <v>12</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0.16700000000000001</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12" s="6">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" s="7">
@@ -1054,6 +1093,36 @@
       <c r="E13">
         <v>4</v>
       </c>
+      <c r="F13">
+        <v>113</v>
+      </c>
+      <c r="G13">
+        <v>113</v>
+      </c>
+      <c r="H13">
+        <v>35</v>
+      </c>
+      <c r="I13" s="6">
+        <v>0.31</v>
+      </c>
+      <c r="J13">
+        <v>4</v>
+      </c>
+      <c r="K13" s="5">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13" s="6">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="7">
@@ -1071,6 +1140,36 @@
       <c r="E14">
         <v>9</v>
       </c>
+      <c r="F14">
+        <v>895</v>
+      </c>
+      <c r="G14">
+        <v>895</v>
+      </c>
+      <c r="H14">
+        <v>280</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0.313</v>
+      </c>
+      <c r="J14">
+        <v>50</v>
+      </c>
+      <c r="K14" s="5">
+        <v>5.6000000000000001E-2</v>
+      </c>
+      <c r="L14">
+        <v>8</v>
+      </c>
+      <c r="M14" s="5">
+        <v>8.8999999999999999E-3</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" s="7">
@@ -1136,7 +1235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" s="7">
         <v>46188</v>
       </c>
@@ -1149,6 +1248,194 @@
       <c r="D17">
         <v>10</v>
       </c>
+      <c r="F17">
+        <v>10</v>
+      </c>
+      <c r="G17">
+        <v>10</v>
+      </c>
+      <c r="J17">
+        <v>4</v>
+      </c>
+      <c r="K17" s="6">
+        <v>0.4</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A18" s="7">
+        <v>46190</v>
+      </c>
+      <c r="B18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18" s="6">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A19" s="7">
+        <v>46190</v>
+      </c>
+      <c r="B19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" t="s">
+        <v>33</v>
+      </c>
+      <c r="D19">
+        <v>7</v>
+      </c>
+      <c r="F19">
+        <v>7</v>
+      </c>
+      <c r="G19">
+        <v>7</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19" s="6">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A20" s="7">
+        <v>46191</v>
+      </c>
+      <c r="B20" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20">
+        <v>72</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>72</v>
+      </c>
+      <c r="G20">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A21" s="7">
+        <v>46191</v>
+      </c>
+      <c r="B21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" t="s">
+        <v>41</v>
+      </c>
+      <c r="D21">
+        <v>84</v>
+      </c>
+      <c r="E21">
+        <v>-29</v>
+      </c>
+      <c r="F21">
+        <v>84</v>
+      </c>
+      <c r="G21">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A22" s="7">
+        <v>46191</v>
+      </c>
+      <c r="B22" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" t="s">
+        <v>40</v>
+      </c>
+      <c r="D22">
+        <v>911</v>
+      </c>
+      <c r="E22">
+        <v>16</v>
+      </c>
+      <c r="F22">
+        <v>911</v>
+      </c>
+      <c r="G22">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A23" s="7">
+        <v>46192</v>
+      </c>
+      <c r="B23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A24" s="7">
+        <v>46192</v>
+      </c>
+      <c r="B24" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" t="s">
+        <v>33</v>
+      </c>
+      <c r="D24">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A25" s="7"/>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A26" s="7"/>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A27" s="7"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:M4" xr:uid="{00000000-0009-0000-0000-000000000000}"/>

--- a/database.xlsx
+++ b/database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/serena/Desktop/Hunter CRM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE0DFFFF-D31A-EA4B-9214-60CA17BC0F6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B05250FA-1649-E245-92D4-28D0DA72B1FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="46">
   <si>
     <t>date</t>
   </si>
@@ -166,6 +166,15 @@
   </si>
   <si>
     <t>EDM #5: Off-Road Capability (Reservation)</t>
+  </si>
+  <si>
+    <t>EDM #6: JAC Genuine Accessories (Reserve)</t>
+  </si>
+  <si>
+    <t>EDM #5: Off-Road Capability (Build)</t>
+  </si>
+  <si>
+    <t>EDM #5: Off-Road Capability (EOI)</t>
   </si>
 </sst>
 </file>
@@ -234,7 +243,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -251,6 +260,10 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -553,7 +566,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O27"/>
+  <dimension ref="A1:O31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1235,7 +1248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" s="7">
         <v>46188</v>
       </c>
@@ -1267,7 +1280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18" s="7">
         <v>46190</v>
       </c>
@@ -1299,7 +1312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A19" s="7">
         <v>46190</v>
       </c>
@@ -1331,111 +1344,391 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A20" s="7">
+    <row r="20" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="8">
         <v>46191</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="9">
         <v>72</v>
       </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20">
+      <c r="E20" s="9">
+        <v>0</v>
+      </c>
+      <c r="F20" s="9">
         <v>72</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="9">
         <v>72</v>
       </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A21" s="7">
+      <c r="H20" s="9">
+        <v>48</v>
+      </c>
+      <c r="I20" s="10">
+        <v>0.66700000000000004</v>
+      </c>
+      <c r="J20" s="9">
+        <v>22</v>
+      </c>
+      <c r="K20" s="10">
+        <v>0.30599999999999999</v>
+      </c>
+      <c r="L20" s="9">
+        <v>0</v>
+      </c>
+      <c r="M20" s="11">
+        <v>0</v>
+      </c>
+      <c r="N20" s="9">
+        <v>0</v>
+      </c>
+      <c r="O20" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="8">
         <v>46191</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="9">
         <v>84</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="9">
         <v>-29</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="9">
         <v>84</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="9">
         <v>84</v>
       </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A22" s="7">
+      <c r="H21" s="9">
+        <v>17</v>
+      </c>
+      <c r="I21" s="10">
+        <v>0.20200000000000001</v>
+      </c>
+      <c r="J21" s="9">
+        <v>7</v>
+      </c>
+      <c r="K21" s="10">
+        <v>8.3000000000000004E-2</v>
+      </c>
+      <c r="L21" s="9">
+        <v>0</v>
+      </c>
+      <c r="M21" s="11">
+        <v>0</v>
+      </c>
+      <c r="N21" s="9">
+        <v>0</v>
+      </c>
+      <c r="O21" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="8">
         <v>46191</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="9">
         <v>911</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="9">
         <v>16</v>
       </c>
-      <c r="F22">
+      <c r="F22" s="9">
         <v>911</v>
       </c>
-      <c r="G22">
+      <c r="G22" s="9">
         <v>911</v>
       </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A23" s="7">
+      <c r="H22" s="9">
+        <v>308</v>
+      </c>
+      <c r="I22" s="10">
+        <v>0.33800000000000002</v>
+      </c>
+      <c r="J22" s="9">
+        <v>81</v>
+      </c>
+      <c r="K22" s="10">
+        <v>8.8999999999999996E-2</v>
+      </c>
+      <c r="L22" s="9">
+        <v>9</v>
+      </c>
+      <c r="M22" s="10">
+        <v>8.8000000000000005E-3</v>
+      </c>
+      <c r="N22" s="9">
+        <v>0</v>
+      </c>
+      <c r="O22" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="8">
         <v>46192</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="9">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A24" s="7">
+      <c r="F23" s="9">
+        <v>1</v>
+      </c>
+      <c r="G23" s="9">
+        <v>1</v>
+      </c>
+      <c r="J23" s="9">
+        <v>0</v>
+      </c>
+      <c r="K23" s="11">
+        <v>0</v>
+      </c>
+      <c r="L23" s="9">
+        <v>0</v>
+      </c>
+      <c r="M23" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="8">
         <v>46192</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="9">
         <v>9</v>
       </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A25" s="7"/>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A26" s="7"/>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A27" s="7"/>
+      <c r="F24" s="9">
+        <v>9</v>
+      </c>
+      <c r="G24" s="9">
+        <v>9</v>
+      </c>
+      <c r="J24" s="9">
+        <v>4</v>
+      </c>
+      <c r="K24" s="10">
+        <v>0.44400000000000001</v>
+      </c>
+      <c r="L24" s="9">
+        <v>0</v>
+      </c>
+      <c r="M24" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="8">
+        <v>46195</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D25" s="9">
+        <v>3</v>
+      </c>
+      <c r="F25" s="9">
+        <v>3</v>
+      </c>
+      <c r="G25" s="9">
+        <v>3</v>
+      </c>
+      <c r="J25" s="9">
+        <v>1</v>
+      </c>
+      <c r="K25" s="10">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="L25" s="9">
+        <v>0</v>
+      </c>
+      <c r="M25" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="8">
+        <v>46195</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D26" s="9">
+        <v>9</v>
+      </c>
+      <c r="F26" s="9">
+        <v>9</v>
+      </c>
+      <c r="G26" s="9">
+        <v>8</v>
+      </c>
+      <c r="J26" s="9">
+        <f>8*37.5%</f>
+        <v>3</v>
+      </c>
+      <c r="K26" s="10">
+        <v>0.375</v>
+      </c>
+      <c r="L26" s="9">
+        <v>0</v>
+      </c>
+      <c r="M26" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="8">
+        <v>46197</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D27" s="9">
+        <v>6</v>
+      </c>
+      <c r="F27" s="9">
+        <v>6</v>
+      </c>
+      <c r="G27" s="9">
+        <v>5</v>
+      </c>
+      <c r="J27" s="9">
+        <v>1</v>
+      </c>
+      <c r="K27" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="L27" s="9">
+        <v>0</v>
+      </c>
+      <c r="M27" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A28" s="7">
+        <v>46198</v>
+      </c>
+      <c r="B28" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" t="s">
+        <v>43</v>
+      </c>
+      <c r="D28">
+        <v>76</v>
+      </c>
+      <c r="E28">
+        <v>4</v>
+      </c>
+      <c r="F28">
+        <v>76</v>
+      </c>
+      <c r="G28">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A29" s="7">
+        <v>46198</v>
+      </c>
+      <c r="B29" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" t="s">
+        <v>44</v>
+      </c>
+      <c r="D29">
+        <v>118</v>
+      </c>
+      <c r="E29">
+        <f>118-84</f>
+        <v>34</v>
+      </c>
+      <c r="F29">
+        <v>118</v>
+      </c>
+      <c r="G29">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A30" s="7">
+        <v>46198</v>
+      </c>
+      <c r="B30" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" t="s">
+        <v>45</v>
+      </c>
+      <c r="D30">
+        <v>922</v>
+      </c>
+      <c r="E30">
+        <v>11</v>
+      </c>
+      <c r="F30">
+        <v>922</v>
+      </c>
+      <c r="G30">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A31" s="7">
+        <v>46199</v>
+      </c>
+      <c r="B31" t="s">
+        <v>32</v>
+      </c>
+      <c r="C31" t="s">
+        <v>33</v>
+      </c>
+      <c r="D31">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:M4" xr:uid="{00000000-0009-0000-0000-000000000000}"/>

--- a/database.xlsx
+++ b/database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/serena/Desktop/Hunter CRM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B05250FA-1649-E245-92D4-28D0DA72B1FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77AA373B-D1F2-E345-BD91-162ED7F2388C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="48">
   <si>
     <t>date</t>
   </si>
@@ -175,6 +175,12 @@
   </si>
   <si>
     <t>EDM #5: Off-Road Capability (EOI)</t>
+  </si>
+  <si>
+    <t>EDM #7: Hunter Specs Announced (Reserve)</t>
+  </si>
+  <si>
+    <t>EDM #7: Hunter Specs Announced (EOI)</t>
   </si>
 </sst>
 </file>
@@ -260,8 +266,8 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
@@ -566,7 +572,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O31"/>
+  <dimension ref="A1:O38"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1344,376 +1350,448 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="8">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A20" s="7">
         <v>46191</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C20" t="s">
         <v>42</v>
       </c>
-      <c r="D20" s="9">
+      <c r="D20">
         <v>72</v>
       </c>
-      <c r="E20" s="9">
-        <v>0</v>
-      </c>
-      <c r="F20" s="9">
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
         <v>72</v>
       </c>
-      <c r="G20" s="9">
+      <c r="G20">
         <v>72</v>
       </c>
-      <c r="H20" s="9">
+      <c r="H20">
         <v>48</v>
       </c>
-      <c r="I20" s="10">
+      <c r="I20" s="5">
         <v>0.66700000000000004</v>
       </c>
-      <c r="J20" s="9">
+      <c r="J20">
         <v>22</v>
       </c>
-      <c r="K20" s="10">
+      <c r="K20" s="5">
         <v>0.30599999999999999</v>
       </c>
-      <c r="L20" s="9">
-        <v>0</v>
-      </c>
-      <c r="M20" s="11">
-        <v>0</v>
-      </c>
-      <c r="N20" s="9">
-        <v>0</v>
-      </c>
-      <c r="O20" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="8">
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20" s="6">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A21" s="7">
         <v>46191</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" t="s">
         <v>7</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" t="s">
         <v>41</v>
       </c>
-      <c r="D21" s="9">
+      <c r="D21">
         <v>84</v>
       </c>
-      <c r="E21" s="9">
+      <c r="E21">
         <v>-29</v>
       </c>
-      <c r="F21" s="9">
+      <c r="F21">
         <v>84</v>
       </c>
-      <c r="G21" s="9">
+      <c r="G21">
         <v>84</v>
       </c>
-      <c r="H21" s="9">
+      <c r="H21">
         <v>17</v>
       </c>
-      <c r="I21" s="10">
+      <c r="I21" s="5">
         <v>0.20200000000000001</v>
       </c>
-      <c r="J21" s="9">
+      <c r="J21">
         <v>7</v>
       </c>
-      <c r="K21" s="10">
+      <c r="K21" s="5">
         <v>8.3000000000000004E-2</v>
       </c>
-      <c r="L21" s="9">
-        <v>0</v>
-      </c>
-      <c r="M21" s="11">
-        <v>0</v>
-      </c>
-      <c r="N21" s="9">
-        <v>0</v>
-      </c>
-      <c r="O21" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="8">
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21" s="6">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A22" s="7">
         <v>46191</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" t="s">
         <v>8</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" t="s">
         <v>40</v>
       </c>
-      <c r="D22" s="9">
+      <c r="D22">
         <v>911</v>
       </c>
-      <c r="E22" s="9">
+      <c r="E22">
         <v>16</v>
       </c>
-      <c r="F22" s="9">
+      <c r="F22">
         <v>911</v>
       </c>
-      <c r="G22" s="9">
+      <c r="G22">
         <v>911</v>
       </c>
-      <c r="H22" s="9">
+      <c r="H22">
         <v>308</v>
       </c>
-      <c r="I22" s="10">
+      <c r="I22" s="5">
         <v>0.33800000000000002</v>
       </c>
-      <c r="J22" s="9">
+      <c r="J22">
         <v>81</v>
       </c>
-      <c r="K22" s="10">
+      <c r="K22" s="5">
         <v>8.8999999999999996E-2</v>
       </c>
-      <c r="L22" s="9">
+      <c r="L22">
         <v>9</v>
       </c>
-      <c r="M22" s="10">
+      <c r="M22" s="5">
         <v>8.8000000000000005E-3</v>
       </c>
-      <c r="N22" s="9">
-        <v>0</v>
-      </c>
-      <c r="O22" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="8">
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A23" s="7">
         <v>46192</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" t="s">
         <v>31</v>
       </c>
-      <c r="D23" s="9">
+      <c r="D23">
         <v>1</v>
       </c>
-      <c r="F23" s="9">
+      <c r="F23">
         <v>1</v>
       </c>
-      <c r="G23" s="9">
+      <c r="G23">
         <v>1</v>
       </c>
-      <c r="J23" s="9">
-        <v>0</v>
-      </c>
-      <c r="K23" s="11">
-        <v>0</v>
-      </c>
-      <c r="L23" s="9">
-        <v>0</v>
-      </c>
-      <c r="M23" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="8">
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23" s="6">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A24" s="7">
         <v>46192</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" t="s">
         <v>32</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" t="s">
         <v>33</v>
       </c>
-      <c r="D24" s="9">
+      <c r="D24">
         <v>9</v>
       </c>
-      <c r="F24" s="9">
+      <c r="F24">
         <v>9</v>
       </c>
-      <c r="G24" s="9">
+      <c r="G24">
         <v>9</v>
       </c>
-      <c r="J24" s="9">
+      <c r="J24">
         <v>4</v>
       </c>
-      <c r="K24" s="10">
+      <c r="K24" s="5">
         <v>0.44400000000000001</v>
       </c>
-      <c r="L24" s="9">
-        <v>0</v>
-      </c>
-      <c r="M24" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="8">
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A25" s="7">
         <v>46195</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="B25" t="s">
         <v>30</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" t="s">
         <v>31</v>
       </c>
-      <c r="D25" s="9">
+      <c r="D25">
         <v>3</v>
       </c>
-      <c r="F25" s="9">
+      <c r="F25">
         <v>3</v>
       </c>
-      <c r="G25" s="9">
+      <c r="G25">
         <v>3</v>
       </c>
-      <c r="J25" s="9">
+      <c r="J25">
         <v>1</v>
       </c>
-      <c r="K25" s="10">
+      <c r="K25" s="5">
         <v>0.33300000000000002</v>
       </c>
-      <c r="L25" s="9">
-        <v>0</v>
-      </c>
-      <c r="M25" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="8">
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A26" s="7">
         <v>46195</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="B26" t="s">
         <v>32</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="C26" t="s">
         <v>33</v>
       </c>
-      <c r="D26" s="9">
+      <c r="D26">
         <v>9</v>
       </c>
-      <c r="F26" s="9">
+      <c r="F26">
         <v>9</v>
       </c>
-      <c r="G26" s="9">
+      <c r="G26">
         <v>8</v>
       </c>
-      <c r="J26" s="9">
+      <c r="J26">
         <f>8*37.5%</f>
         <v>3</v>
       </c>
-      <c r="K26" s="10">
+      <c r="K26" s="5">
         <v>0.375</v>
       </c>
-      <c r="L26" s="9">
-        <v>0</v>
-      </c>
-      <c r="M26" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="8">
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A27" s="7">
         <v>46197</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="B27" t="s">
         <v>32</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="C27" t="s">
         <v>33</v>
       </c>
-      <c r="D27" s="9">
+      <c r="D27">
         <v>6</v>
       </c>
-      <c r="F27" s="9">
+      <c r="F27">
         <v>6</v>
       </c>
-      <c r="G27" s="9">
+      <c r="G27">
         <v>5</v>
       </c>
-      <c r="J27" s="9">
+      <c r="J27">
         <v>1</v>
       </c>
-      <c r="K27" s="11">
+      <c r="K27" s="6">
         <v>0.2</v>
       </c>
-      <c r="L27" s="9">
-        <v>0</v>
-      </c>
-      <c r="M27" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A28" s="7">
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="9">
         <v>46198</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="8">
         <v>76</v>
       </c>
-      <c r="E28">
+      <c r="E28" s="8">
         <v>4</v>
       </c>
-      <c r="F28">
+      <c r="F28" s="8">
         <v>76</v>
       </c>
-      <c r="G28">
+      <c r="G28" s="8">
         <v>76</v>
       </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A29" s="7">
+      <c r="H28" s="8">
+        <v>54</v>
+      </c>
+      <c r="I28" s="10">
+        <v>0.71099999999999997</v>
+      </c>
+      <c r="J28" s="8">
+        <v>34</v>
+      </c>
+      <c r="K28" s="10">
+        <v>0.44700000000000001</v>
+      </c>
+      <c r="L28" s="8">
+        <v>0</v>
+      </c>
+      <c r="M28" s="11">
+        <v>0</v>
+      </c>
+      <c r="N28" s="8">
+        <v>0</v>
+      </c>
+      <c r="O28" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="9">
         <v>46198</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="8">
         <v>118</v>
       </c>
-      <c r="E29">
+      <c r="E29" s="8">
         <f>118-84</f>
         <v>34</v>
       </c>
-      <c r="F29">
+      <c r="F29" s="8">
         <v>118</v>
       </c>
-      <c r="G29">
+      <c r="G29" s="8">
         <v>118</v>
       </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A30" s="7">
+      <c r="H29" s="8">
+        <v>34</v>
+      </c>
+      <c r="I29" s="10">
+        <v>0.28799999999999998</v>
+      </c>
+      <c r="J29" s="8">
+        <v>12</v>
+      </c>
+      <c r="K29" s="10">
+        <v>0.10199999999999999</v>
+      </c>
+      <c r="L29" s="8">
+        <v>2</v>
+      </c>
+      <c r="M29" s="10">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="N29" s="8">
+        <v>0</v>
+      </c>
+      <c r="O29" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="9">
         <v>46198</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D30">
+      <c r="D30" s="8">
         <v>922</v>
       </c>
-      <c r="E30">
+      <c r="E30" s="8">
         <v>11</v>
       </c>
-      <c r="F30">
+      <c r="F30" s="8">
         <v>922</v>
       </c>
-      <c r="G30">
+      <c r="G30" s="8">
         <v>922</v>
+      </c>
+      <c r="H30" s="8">
+        <v>313</v>
+      </c>
+      <c r="I30" s="10">
+        <v>0.33900000000000002</v>
+      </c>
+      <c r="J30" s="8">
+        <v>87</v>
+      </c>
+      <c r="K30" s="10">
+        <v>9.4E-2</v>
+      </c>
+      <c r="L30" s="8">
+        <v>8</v>
+      </c>
+      <c r="M30" s="10">
+        <v>8.6999999999999994E-3</v>
+      </c>
+      <c r="N30" s="8">
+        <v>0</v>
+      </c>
+      <c r="O30" s="11">
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.2">
@@ -1728,6 +1806,113 @@
       </c>
       <c r="D31">
         <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A32" s="7">
+        <v>46202</v>
+      </c>
+      <c r="B32" t="s">
+        <v>30</v>
+      </c>
+      <c r="C32" t="s">
+        <v>31</v>
+      </c>
+      <c r="D32" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33" s="7">
+        <v>46202</v>
+      </c>
+      <c r="B33" t="s">
+        <v>32</v>
+      </c>
+      <c r="C33" t="s">
+        <v>33</v>
+      </c>
+      <c r="D33" s="8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A34" s="7">
+        <v>46204</v>
+      </c>
+      <c r="B34" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" t="s">
+        <v>31</v>
+      </c>
+      <c r="D34" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A35" s="7">
+        <v>46204</v>
+      </c>
+      <c r="B35" t="s">
+        <v>32</v>
+      </c>
+      <c r="C35" t="s">
+        <v>33</v>
+      </c>
+      <c r="D35" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A36" s="9">
+        <v>46198</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" t="s">
+        <v>46</v>
+      </c>
+      <c r="D36" s="8">
+        <v>80</v>
+      </c>
+      <c r="E36">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A37" s="9">
+        <v>46198</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" t="s">
+        <v>47</v>
+      </c>
+      <c r="D37" s="8">
+        <v>121</v>
+      </c>
+      <c r="E37">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A38" s="9">
+        <v>46198</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" t="s">
+        <v>47</v>
+      </c>
+      <c r="D38">
+        <v>929</v>
+      </c>
+      <c r="E38">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/database.xlsx
+++ b/database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/serena/Desktop/Hunter CRM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77AA373B-D1F2-E345-BD91-162ED7F2388C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6766F0D-E259-404A-A057-D4ABE723E756}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="56">
   <si>
     <t>date</t>
   </si>
@@ -181,6 +181,30 @@
   </si>
   <si>
     <t>EDM #7: Hunter Specs Announced (EOI)</t>
+  </si>
+  <si>
+    <t>Hunter Brochure is here (Reserve)</t>
+  </si>
+  <si>
+    <t>Hunter Brochure is here (EOI &amp; Build)</t>
+  </si>
+  <si>
+    <t>EDM #7: Hunter Specs Announced (Build)</t>
+  </si>
+  <si>
+    <t>EDM #8: Hunter Price Announced (Reserve)</t>
+  </si>
+  <si>
+    <t>EDM #8: Hunter Price Announced (Build)</t>
+  </si>
+  <si>
+    <t>EDM #8: Hunter Price Announced (EOI)</t>
+  </si>
+  <si>
+    <t>Hunter Pricing is here (Reserve)</t>
+  </si>
+  <si>
+    <t>Hunter Pricing is here (EOI &amp; Build)</t>
   </si>
 </sst>
 </file>
@@ -249,7 +273,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -266,10 +290,6 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -572,7 +592,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O38"/>
+  <dimension ref="A1:O46"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1652,145 +1672,145 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="9">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A28" s="7">
         <v>46198</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="B28" t="s">
         <v>6</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" t="s">
         <v>43</v>
       </c>
-      <c r="D28" s="8">
+      <c r="D28">
         <v>76</v>
       </c>
-      <c r="E28" s="8">
+      <c r="E28">
         <v>4</v>
       </c>
-      <c r="F28" s="8">
+      <c r="F28">
         <v>76</v>
       </c>
-      <c r="G28" s="8">
+      <c r="G28">
         <v>76</v>
       </c>
-      <c r="H28" s="8">
+      <c r="H28">
         <v>54</v>
       </c>
-      <c r="I28" s="10">
+      <c r="I28" s="5">
         <v>0.71099999999999997</v>
       </c>
-      <c r="J28" s="8">
+      <c r="J28">
         <v>34</v>
       </c>
-      <c r="K28" s="10">
+      <c r="K28" s="5">
         <v>0.44700000000000001</v>
       </c>
-      <c r="L28" s="8">
-        <v>0</v>
-      </c>
-      <c r="M28" s="11">
-        <v>0</v>
-      </c>
-      <c r="N28" s="8">
-        <v>0</v>
-      </c>
-      <c r="O28" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="9">
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28" s="6">
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A29" s="7">
         <v>46198</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="B29" t="s">
         <v>7</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="C29" t="s">
         <v>44</v>
       </c>
-      <c r="D29" s="8">
+      <c r="D29">
         <v>118</v>
       </c>
-      <c r="E29" s="8">
+      <c r="E29">
         <f>118-84</f>
         <v>34</v>
       </c>
-      <c r="F29" s="8">
+      <c r="F29">
         <v>118</v>
       </c>
-      <c r="G29" s="8">
+      <c r="G29">
         <v>118</v>
       </c>
-      <c r="H29" s="8">
+      <c r="H29">
         <v>34</v>
       </c>
-      <c r="I29" s="10">
+      <c r="I29" s="5">
         <v>0.28799999999999998</v>
       </c>
-      <c r="J29" s="8">
+      <c r="J29">
         <v>12</v>
       </c>
-      <c r="K29" s="10">
+      <c r="K29" s="5">
         <v>0.10199999999999999</v>
       </c>
-      <c r="L29" s="8">
+      <c r="L29">
         <v>2</v>
       </c>
-      <c r="M29" s="10">
+      <c r="M29" s="5">
         <v>1.7000000000000001E-2</v>
       </c>
-      <c r="N29" s="8">
-        <v>0</v>
-      </c>
-      <c r="O29" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="9">
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A30" s="7">
         <v>46198</v>
       </c>
-      <c r="B30" s="8" t="s">
+      <c r="B30" t="s">
         <v>8</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="C30" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="8">
+      <c r="D30">
         <v>922</v>
       </c>
-      <c r="E30" s="8">
+      <c r="E30">
         <v>11</v>
       </c>
-      <c r="F30" s="8">
+      <c r="F30">
         <v>922</v>
       </c>
-      <c r="G30" s="8">
+      <c r="G30">
         <v>922</v>
       </c>
-      <c r="H30" s="8">
+      <c r="H30">
         <v>313</v>
       </c>
-      <c r="I30" s="10">
+      <c r="I30" s="5">
         <v>0.33900000000000002</v>
       </c>
-      <c r="J30" s="8">
+      <c r="J30">
         <v>87</v>
       </c>
-      <c r="K30" s="10">
+      <c r="K30" s="5">
         <v>9.4E-2</v>
       </c>
-      <c r="L30" s="8">
+      <c r="L30">
         <v>8</v>
       </c>
-      <c r="M30" s="10">
+      <c r="M30" s="5">
         <v>8.6999999999999994E-3</v>
       </c>
-      <c r="N30" s="8">
-        <v>0</v>
-      </c>
-      <c r="O30" s="11">
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30" s="6">
         <v>0</v>
       </c>
     </row>
@@ -1818,11 +1838,11 @@
       <c r="C32" t="s">
         <v>31</v>
       </c>
-      <c r="D32" s="8">
+      <c r="D32">
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A33" s="7">
         <v>46202</v>
       </c>
@@ -1832,11 +1852,11 @@
       <c r="C33" t="s">
         <v>33</v>
       </c>
-      <c r="D33" s="8">
+      <c r="D33">
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A34" s="7">
         <v>46204</v>
       </c>
@@ -1846,11 +1866,11 @@
       <c r="C34" t="s">
         <v>31</v>
       </c>
-      <c r="D34" s="8">
+      <c r="D34">
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A35" s="7">
         <v>46204</v>
       </c>
@@ -1860,49 +1880,109 @@
       <c r="C35" t="s">
         <v>33</v>
       </c>
-      <c r="D35" s="8">
+      <c r="D35">
         <v>6</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A36" s="9">
-        <v>46198</v>
-      </c>
-      <c r="B36" s="8" t="s">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A36" s="7">
+        <v>46206</v>
+      </c>
+      <c r="B36" t="s">
         <v>6</v>
       </c>
       <c r="C36" t="s">
         <v>46</v>
       </c>
-      <c r="D36" s="8">
+      <c r="D36">
         <v>80</v>
       </c>
       <c r="E36">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A37" s="9">
-        <v>46198</v>
-      </c>
-      <c r="B37" s="8" t="s">
+      <c r="F36">
+        <v>80</v>
+      </c>
+      <c r="G36">
+        <v>80</v>
+      </c>
+      <c r="H36">
+        <v>56</v>
+      </c>
+      <c r="I36" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="J36">
+        <v>46</v>
+      </c>
+      <c r="K36" s="5">
+        <v>0.57499999999999996</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36" s="6">
+        <v>0</v>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A37" s="7">
+        <v>46206</v>
+      </c>
+      <c r="B37" t="s">
         <v>7</v>
       </c>
       <c r="C37" t="s">
-        <v>47</v>
-      </c>
-      <c r="D37" s="8">
+        <v>50</v>
+      </c>
+      <c r="D37">
         <v>121</v>
       </c>
       <c r="E37">
         <v>3</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A38" s="9">
-        <v>46198</v>
-      </c>
-      <c r="B38" s="8" t="s">
+      <c r="F37">
+        <v>121</v>
+      </c>
+      <c r="G37">
+        <v>121</v>
+      </c>
+      <c r="H37">
+        <v>42</v>
+      </c>
+      <c r="I37" s="5">
+        <v>0.34699999999999998</v>
+      </c>
+      <c r="J37">
+        <v>23</v>
+      </c>
+      <c r="K37" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37" s="6">
+        <v>0</v>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A38" s="7">
+        <v>46206</v>
+      </c>
+      <c r="B38" t="s">
         <v>8</v>
       </c>
       <c r="C38" t="s">
@@ -1914,6 +1994,191 @@
       <c r="E38">
         <v>7</v>
       </c>
+      <c r="F38">
+        <v>929</v>
+      </c>
+      <c r="G38">
+        <v>928</v>
+      </c>
+      <c r="H38">
+        <v>321</v>
+      </c>
+      <c r="I38" s="5">
+        <v>0.34599999999999997</v>
+      </c>
+      <c r="J38">
+        <v>172</v>
+      </c>
+      <c r="K38" s="5">
+        <v>0.185</v>
+      </c>
+      <c r="L38">
+        <v>8</v>
+      </c>
+      <c r="M38" s="5">
+        <v>8.6E-3</v>
+      </c>
+      <c r="N38">
+        <v>1</v>
+      </c>
+      <c r="O38" s="5">
+        <v>1.1000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A39" s="7">
+        <v>46206</v>
+      </c>
+      <c r="B39" t="s">
+        <v>30</v>
+      </c>
+      <c r="C39" t="s">
+        <v>48</v>
+      </c>
+      <c r="D39">
+        <v>80</v>
+      </c>
+      <c r="F39">
+        <v>80</v>
+      </c>
+      <c r="G39">
+        <v>79</v>
+      </c>
+      <c r="J39">
+        <v>50</v>
+      </c>
+      <c r="K39" s="5">
+        <v>0.63300000000000001</v>
+      </c>
+      <c r="L39">
+        <v>1</v>
+      </c>
+      <c r="M39" s="5">
+        <v>1.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A40" s="7">
+        <v>46206</v>
+      </c>
+      <c r="B40" t="s">
+        <v>32</v>
+      </c>
+      <c r="C40" t="s">
+        <v>49</v>
+      </c>
+      <c r="D40">
+        <v>854</v>
+      </c>
+      <c r="F40">
+        <v>854</v>
+      </c>
+      <c r="G40">
+        <v>831</v>
+      </c>
+      <c r="J40">
+        <v>492</v>
+      </c>
+      <c r="K40" s="5">
+        <v>0.57599999999999996</v>
+      </c>
+      <c r="L40">
+        <v>14</v>
+      </c>
+      <c r="M40" s="5">
+        <v>1.7000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A41" s="7">
+        <v>46213</v>
+      </c>
+      <c r="B41" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" t="s">
+        <v>51</v>
+      </c>
+      <c r="D41">
+        <v>81</v>
+      </c>
+      <c r="E41">
+        <v>1</v>
+      </c>
+      <c r="I41" s="5"/>
+      <c r="K41" s="5"/>
+      <c r="M41" s="6"/>
+      <c r="N41">
+        <v>1</v>
+      </c>
+      <c r="O41" s="5">
+        <v>0.112</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A42" s="7">
+        <v>46213</v>
+      </c>
+      <c r="B42" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" t="s">
+        <v>52</v>
+      </c>
+      <c r="D42">
+        <v>136</v>
+      </c>
+      <c r="E42">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A43" s="7">
+        <v>46213</v>
+      </c>
+      <c r="B43" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" t="s">
+        <v>53</v>
+      </c>
+      <c r="D43">
+        <v>915</v>
+      </c>
+      <c r="E43">
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A44" s="7">
+        <v>46213</v>
+      </c>
+      <c r="B44" t="s">
+        <v>30</v>
+      </c>
+      <c r="C44" t="s">
+        <v>54</v>
+      </c>
+      <c r="D44">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A45" s="7">
+        <v>46213</v>
+      </c>
+      <c r="B45" t="s">
+        <v>32</v>
+      </c>
+      <c r="C45" t="s">
+        <v>55</v>
+      </c>
+      <c r="D45">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A46" s="7"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:M4" xr:uid="{00000000-0009-0000-0000-000000000000}"/>

--- a/database.xlsx
+++ b/database.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11008"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/serena/Desktop/Hunter CRM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6766F0D-E259-404A-A057-D4ABE723E756}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6831005A-E83A-9D46-9BEA-8A57766FCF99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1827,6 +1827,24 @@
       <c r="D31">
         <v>6</v>
       </c>
+      <c r="F31">
+        <v>6</v>
+      </c>
+      <c r="G31">
+        <v>6</v>
+      </c>
+      <c r="J31">
+        <v>1</v>
+      </c>
+      <c r="K31" s="5">
+        <v>0.16700000000000001</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A32" s="7">
@@ -1841,6 +1859,24 @@
       <c r="D32">
         <v>1</v>
       </c>
+      <c r="F32">
+        <v>1</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32" s="6">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A33" s="7">
@@ -1855,6 +1891,24 @@
       <c r="D33">
         <v>9</v>
       </c>
+      <c r="F33">
+        <v>9</v>
+      </c>
+      <c r="G33">
+        <v>9</v>
+      </c>
+      <c r="J33">
+        <v>3</v>
+      </c>
+      <c r="K33" s="5">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A34" s="7">
@@ -1869,6 +1923,24 @@
       <c r="D34">
         <v>3</v>
       </c>
+      <c r="F34">
+        <v>3</v>
+      </c>
+      <c r="G34">
+        <v>3</v>
+      </c>
+      <c r="J34">
+        <v>1</v>
+      </c>
+      <c r="K34" s="5">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A35" s="7">
@@ -1883,6 +1955,24 @@
       <c r="D35">
         <v>6</v>
       </c>
+      <c r="F35">
+        <v>6</v>
+      </c>
+      <c r="G35">
+        <v>5</v>
+      </c>
+      <c r="J35">
+        <v>2</v>
+      </c>
+      <c r="K35" s="6">
+        <v>0.4</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A36" s="7">
@@ -2105,14 +2195,35 @@
       <c r="E41">
         <v>1</v>
       </c>
-      <c r="I41" s="5"/>
-      <c r="K41" s="5"/>
-      <c r="M41" s="6"/>
+      <c r="F41">
+        <v>81</v>
+      </c>
+      <c r="G41">
+        <v>80</v>
+      </c>
+      <c r="H41">
+        <v>56</v>
+      </c>
+      <c r="I41" s="5">
+        <v>0.7</v>
+      </c>
+      <c r="J41">
+        <v>28</v>
+      </c>
+      <c r="K41" s="5">
+        <v>0.35</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41" s="6">
+        <v>0</v>
+      </c>
       <c r="N41">
         <v>1</v>
       </c>
       <c r="O41" s="5">
-        <v>0.112</v>
+        <v>1.2E-2</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.2">
@@ -2131,6 +2242,36 @@
       <c r="E42">
         <v>15</v>
       </c>
+      <c r="F42">
+        <v>136</v>
+      </c>
+      <c r="G42">
+        <v>136</v>
+      </c>
+      <c r="H42">
+        <v>41</v>
+      </c>
+      <c r="I42" s="5">
+        <v>0.30099999999999999</v>
+      </c>
+      <c r="J42">
+        <v>13</v>
+      </c>
+      <c r="K42" s="5">
+        <v>9.6000000000000002E-2</v>
+      </c>
+      <c r="L42">
+        <v>1</v>
+      </c>
+      <c r="M42" s="5">
+        <v>7.4000000000000003E-3</v>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A43" s="7">
@@ -2148,6 +2289,36 @@
       <c r="E43">
         <v>-14</v>
       </c>
+      <c r="F43">
+        <v>915</v>
+      </c>
+      <c r="G43">
+        <v>913</v>
+      </c>
+      <c r="H43">
+        <v>319</v>
+      </c>
+      <c r="I43" s="5">
+        <v>0.34899999999999998</v>
+      </c>
+      <c r="J43">
+        <v>92</v>
+      </c>
+      <c r="K43" s="5">
+        <v>0.10100000000000001</v>
+      </c>
+      <c r="L43">
+        <v>4</v>
+      </c>
+      <c r="M43" s="5">
+        <v>4.4000000000000003E-3</v>
+      </c>
+      <c r="N43">
+        <v>2</v>
+      </c>
+      <c r="O43" s="5">
+        <v>2.2000000000000001E-3</v>
+      </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A44" s="7">
@@ -2162,6 +2333,24 @@
       <c r="D44">
         <v>80</v>
       </c>
+      <c r="F44">
+        <v>80</v>
+      </c>
+      <c r="G44">
+        <v>79</v>
+      </c>
+      <c r="J44">
+        <v>47</v>
+      </c>
+      <c r="K44" s="5">
+        <v>0.58199999999999996</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A45" s="7">
@@ -2175,6 +2364,24 @@
       </c>
       <c r="D45">
         <v>849</v>
+      </c>
+      <c r="F45">
+        <v>849</v>
+      </c>
+      <c r="G45">
+        <v>824</v>
+      </c>
+      <c r="J45">
+        <v>443</v>
+      </c>
+      <c r="K45" s="5">
+        <v>0.53800000000000003</v>
+      </c>
+      <c r="L45">
+        <v>14</v>
+      </c>
+      <c r="M45" s="5">
+        <v>1.7000000000000001E-2</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.2">

--- a/database.xlsx
+++ b/database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/serena/Desktop/Hunter CRM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6831005A-E83A-9D46-9BEA-8A57766FCF99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89B0DE9F-AADE-C442-8B06-5F9776C51D94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="audience_daily_snapshot" sheetId="1" r:id="rId1"/>
@@ -183,12 +183,6 @@
     <t>EDM #7: Hunter Specs Announced (EOI)</t>
   </si>
   <si>
-    <t>Hunter Brochure is here (Reserve)</t>
-  </si>
-  <si>
-    <t>Hunter Brochure is here (EOI &amp; Build)</t>
-  </si>
-  <si>
     <t>EDM #7: Hunter Specs Announced (Build)</t>
   </si>
   <si>
@@ -201,10 +195,16 @@
     <t>EDM #8: Hunter Price Announced (EOI)</t>
   </si>
   <si>
-    <t>Hunter Pricing is here (Reserve)</t>
-  </si>
-  <si>
-    <t>Hunter Pricing is here (EOI &amp; Build)</t>
+    <t>SMS #2 Hunter Brochure is here (Reserve)</t>
+  </si>
+  <si>
+    <t>SMS #2 Hunter Brochure is here (EOI &amp; Build)</t>
+  </si>
+  <si>
+    <t>SMS #3 Hunter Pricing is here (Reserve)</t>
+  </si>
+  <si>
+    <t>SMS #3 Hunter Pricing is here (EOI &amp; Build)</t>
   </si>
 </sst>
 </file>
@@ -2029,7 +2029,7 @@
         <v>7</v>
       </c>
       <c r="C37" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D37">
         <v>121</v>
@@ -2123,7 +2123,7 @@
         <v>30</v>
       </c>
       <c r="C39" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D39">
         <v>80</v>
@@ -2155,7 +2155,7 @@
         <v>32</v>
       </c>
       <c r="C40" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D40">
         <v>854</v>
@@ -2187,7 +2187,7 @@
         <v>6</v>
       </c>
       <c r="C41" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D41">
         <v>81</v>
@@ -2234,7 +2234,7 @@
         <v>7</v>
       </c>
       <c r="C42" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D42">
         <v>136</v>
@@ -2281,7 +2281,7 @@
         <v>8</v>
       </c>
       <c r="C43" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D43">
         <v>915</v>
